--- a/Result/profitability/3059.xlsx
+++ b/Result/profitability/3059.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>0.36625</v>
+        <v>0.37875</v>
       </c>
       <c r="N2" t="n">
-        <v>24.12875</v>
+        <v>24.13375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.48625</v>
+        <v>0.495</v>
       </c>
       <c r="N3" t="n">
-        <v>22.455</v>
+        <v>22.27875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7262500000000001</v>
+        <v>0.74125</v>
       </c>
       <c r="N4" t="n">
-        <v>20.83875</v>
+        <v>20.81875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.855</v>
+        <v>0.8575</v>
       </c>
       <c r="N5" t="n">
-        <v>19.1925</v>
+        <v>18.90875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9037500000000001</v>
+        <v>0.90625</v>
       </c>
       <c r="N6" t="n">
-        <v>17.46</v>
+        <v>17.695</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9425</v>
+        <v>0.9575</v>
       </c>
       <c r="N7" t="n">
-        <v>16.4725</v>
+        <v>16.8025</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.08</v>
       </c>
       <c r="M8" t="n">
-        <v>1.17</v>
+        <v>1.185</v>
       </c>
       <c r="N8" t="n">
-        <v>15.57</v>
+        <v>15.89625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2360</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1733</v>
+      </c>
+      <c r="E75" t="n">
+        <v>627</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>183</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>48</v>
+      </c>
+      <c r="J75" t="n">
+        <v>231</v>
+      </c>
+      <c r="K75" t="n">
+        <v>117</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.13375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4615384615384615</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.609999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1090225563909775</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07876474670367795</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
